--- a/clino_hkk_plane_hkl_accessible.xlsx
+++ b/clino_hkk_plane_hkl_accessible.xlsx
@@ -492,7 +492,7 @@
         <v>95.64363387837386</v>
       </c>
       <c r="F2" t="n">
-        <v>-26.29826809591996</v>
+        <v>-26.29826809592175</v>
       </c>
       <c r="G2" t="n">
         <v>-20.38790312912558</v>
@@ -503,7 +503,7 @@
       <c r="I2" t="n">
         <v>13</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2" t="b">
         <v>1</v>
       </c>
     </row>
@@ -524,7 +524,7 @@
         <v>55.83501608398304</v>
       </c>
       <c r="F3" t="n">
-        <v>-19.02027837354871</v>
+        <v>-19.020278373549</v>
       </c>
       <c r="G3" t="n">
         <v>-20.38790312912558</v>
@@ -535,7 +535,7 @@
       <c r="I3" t="n">
         <v>13</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3" t="b">
         <v>1</v>
       </c>
     </row>
@@ -556,7 +556,7 @@
         <v>85.07298799447561</v>
       </c>
       <c r="F4" t="n">
-        <v>-11.03824946031066</v>
+        <v>-11.03824946031063</v>
       </c>
       <c r="G4" t="n">
         <v>-20.38790312912558</v>
@@ -567,7 +567,7 @@
       <c r="I4" t="n">
         <v>13</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4" t="b">
         <v>1</v>
       </c>
     </row>
@@ -588,7 +588,7 @@
         <v>25.6676293802924</v>
       </c>
       <c r="F5" t="n">
-        <v>5.981178253552143</v>
+        <v>5.981178253548852</v>
       </c>
       <c r="G5" t="n">
         <v>-20.38790312912558</v>
@@ -599,7 +599,7 @@
       <c r="I5" t="n">
         <v>13</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5" t="b">
         <v>1</v>
       </c>
     </row>
@@ -620,7 +620,7 @@
         <v>52.75046453934014</v>
       </c>
       <c r="F6" t="n">
-        <v>5.981270925156059</v>
+        <v>5.981270925153707</v>
       </c>
       <c r="G6" t="n">
         <v>-20.38790312912558</v>
@@ -631,7 +631,7 @@
       <c r="I6" t="n">
         <v>13</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6" t="b">
         <v>1</v>
       </c>
     </row>
@@ -652,7 +652,7 @@
         <v>83.57532188013604</v>
       </c>
       <c r="F7" t="n">
-        <v>5.981319640492675</v>
+        <v>5.981319640491081</v>
       </c>
       <c r="G7" t="n">
         <v>-20.38790312912558</v>
@@ -663,7 +663,7 @@
       <c r="I7" t="n">
         <v>13</v>
       </c>
-      <c r="J7" t="n">
+      <c r="J7" t="b">
         <v>1</v>
       </c>
     </row>
@@ -684,7 +684,7 @@
         <v>60.60812886432331</v>
       </c>
       <c r="F8" t="n">
-        <v>29.07068387597142</v>
+        <v>29.07068387596629</v>
       </c>
       <c r="G8" t="n">
         <v>-20.38790312912558</v>
@@ -695,7 +695,7 @@
       <c r="I8" t="n">
         <v>13</v>
       </c>
-      <c r="J8" t="n">
+      <c r="J8" t="b">
         <v>1</v>
       </c>
     </row>
@@ -716,7 +716,7 @@
         <v>91.16374885469629</v>
       </c>
       <c r="F9" t="n">
-        <v>22.0655059913864</v>
+        <v>22.04628077550482</v>
       </c>
       <c r="G9" t="n">
         <v>-20.38790312912558</v>
@@ -727,7 +727,7 @@
       <c r="I9" t="n">
         <v>13</v>
       </c>
-      <c r="J9" t="n">
+      <c r="J9" t="b">
         <v>1</v>
       </c>
     </row>
@@ -748,7 +748,7 @@
         <v>108.1034567372476</v>
       </c>
       <c r="F10" t="n">
-        <v>35.24744994768259</v>
+        <v>35.2477133397208</v>
       </c>
       <c r="G10" t="n">
         <v>-20.38790312912558</v>
@@ -759,7 +759,7 @@
       <c r="I10" t="n">
         <v>13</v>
       </c>
-      <c r="J10" t="n">
+      <c r="J10" t="b">
         <v>1</v>
       </c>
     </row>
